--- a/outputs/самовыкуп_2склада_парето_31.07.2026.xlsx
+++ b/outputs/самовыкуп_2склада_парето_31.07.2026.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,6 +46,10 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
       <sz val="14"/>
     </font>
     <font>
@@ -61,7 +65,7 @@
       <color rgb="00C00000"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -86,6 +90,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -115,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -148,15 +157,23 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -522,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P114"/>
+  <dimension ref="A1:P121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -6812,6 +6829,133 @@
         <v>1736894</v>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" s="15" t="inlineStr">
+        <is>
+          <t>ИТОГИ ПО ЦВЕТАМ</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>Зона</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>Остаток, шт</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>Себест.сумма, ₽</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>Затраты, ₽</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>Ср. окупаемость, ×</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="16" t="inlineStr">
+        <is>
+          <t>🟢 Действовать (себест.≥2×затрат)</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="C118" s="5" t="n">
+        <v>2799</v>
+      </c>
+      <c r="D118" s="5" t="n">
+        <v>2031215</v>
+      </c>
+      <c r="E118" s="5" t="n">
+        <v>649508</v>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="17" t="inlineStr">
+        <is>
+          <t>🟡 Опционально (1–2×)</t>
+        </is>
+      </c>
+      <c r="B119" s="8" t="n">
+        <v>39</v>
+      </c>
+      <c r="C119" s="8" t="n">
+        <v>3478</v>
+      </c>
+      <c r="D119" s="8" t="n">
+        <v>1330939</v>
+      </c>
+      <c r="E119" s="8" t="n">
+        <v>807070</v>
+      </c>
+      <c r="F119" s="8" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="18" t="inlineStr">
+        <is>
+          <t>🔴 НЕ трогать (затраты&gt;себест.)</t>
+        </is>
+      </c>
+      <c r="B120" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="C120" s="11" t="n">
+        <v>1208</v>
+      </c>
+      <c r="D120" s="11" t="n">
+        <v>200127</v>
+      </c>
+      <c r="E120" s="11" t="n">
+        <v>280316</v>
+      </c>
+      <c r="F120" s="11" t="n">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="19" t="inlineStr">
+        <is>
+          <t>ВСЕГО</t>
+        </is>
+      </c>
+      <c r="B121" s="20" t="n">
+        <v>110</v>
+      </c>
+      <c r="C121" s="20" t="n">
+        <v>7485</v>
+      </c>
+      <c r="D121" s="20" t="n">
+        <v>3562281</v>
+      </c>
+      <c r="E121" s="20" t="n">
+        <v>1736894</v>
+      </c>
+      <c r="F121" s="20" t="n">
+        <v>2.05</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6823,7 +6967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P53"/>
+  <dimension ref="A1:P60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -9697,6 +9841,133 @@
         <v>1295284</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="15" t="inlineStr">
+        <is>
+          <t>ИТОГИ ПО ЦВЕТАМ</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Зона</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Остаток, шт</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Себест.сумма, ₽</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Затраты, ₽</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Ср. окупаемость, ×</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="16" t="inlineStr">
+        <is>
+          <t>🟢 Действовать (себест.≥2×затрат)</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>2275</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>1432562</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>514810</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>2.78</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="17" t="inlineStr">
+        <is>
+          <t>🟡 Опционально (1–2×)</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="C58" s="8" t="n">
+        <v>2074</v>
+      </c>
+      <c r="D58" s="8" t="n">
+        <v>668575</v>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>469325</v>
+      </c>
+      <c r="F58" s="8" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="18" t="inlineStr">
+        <is>
+          <t>🔴 НЕ трогать (затраты&gt;себест.)</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C59" s="11" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D59" s="11" t="n">
+        <v>245027</v>
+      </c>
+      <c r="E59" s="11" t="n">
+        <v>311149</v>
+      </c>
+      <c r="F59" s="11" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="19" t="inlineStr">
+        <is>
+          <t>ВСЕГО</t>
+        </is>
+      </c>
+      <c r="B60" s="20" t="n">
+        <v>49</v>
+      </c>
+      <c r="C60" s="20" t="n">
+        <v>5724</v>
+      </c>
+      <c r="D60" s="20" t="n">
+        <v>2346164</v>
+      </c>
+      <c r="E60" s="20" t="n">
+        <v>1295284</v>
+      </c>
+      <c r="F60" s="20" t="n">
+        <v>1.81</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9708,7 +9979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q114"/>
+  <dimension ref="A1:Q121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -16334,6 +16605,133 @@
         <v>5492124</v>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" s="15" t="inlineStr">
+        <is>
+          <t>ИТОГИ ПО ЦВЕТАМ</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>Зона</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>Остаток, шт</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>Себест.сумма, ₽</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>Затраты, ₽</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>Ср. окупаемость, ×</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="16" t="inlineStr">
+        <is>
+          <t>🟢 Действовать (себест.≥2×затрат)</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="17" t="inlineStr">
+        <is>
+          <t>🟡 Опционально (1–2×)</t>
+        </is>
+      </c>
+      <c r="B119" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C119" s="8" t="n">
+        <v>149</v>
+      </c>
+      <c r="D119" s="8" t="n">
+        <v>199568</v>
+      </c>
+      <c r="E119" s="8" t="n">
+        <v>162023</v>
+      </c>
+      <c r="F119" s="8" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="18" t="inlineStr">
+        <is>
+          <t>🔴 НЕ трогать (затраты&gt;себест.)</t>
+        </is>
+      </c>
+      <c r="B120" s="11" t="n">
+        <v>104</v>
+      </c>
+      <c r="C120" s="11" t="n">
+        <v>7336</v>
+      </c>
+      <c r="D120" s="11" t="n">
+        <v>3362713</v>
+      </c>
+      <c r="E120" s="11" t="n">
+        <v>5330100</v>
+      </c>
+      <c r="F120" s="11" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="19" t="inlineStr">
+        <is>
+          <t>ВСЕГО</t>
+        </is>
+      </c>
+      <c r="B121" s="20" t="n">
+        <v>110</v>
+      </c>
+      <c r="C121" s="20" t="n">
+        <v>7485</v>
+      </c>
+      <c r="D121" s="20" t="n">
+        <v>3562281</v>
+      </c>
+      <c r="E121" s="20" t="n">
+        <v>5492124</v>
+      </c>
+      <c r="F121" s="20" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16345,7 +16743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q53"/>
+  <dimension ref="A1:Q60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -19372,6 +19770,133 @@
         <v>3848695</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="15" t="inlineStr">
+        <is>
+          <t>ИТОГИ ПО ЦВЕТАМ</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Зона</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Остаток, шт</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Себест.сумма, ₽</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Затраты, ₽</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Ср. окупаемость, ×</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="16" t="inlineStr">
+        <is>
+          <t>🟢 Действовать (себест.≥2×затрат)</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="17" t="inlineStr">
+        <is>
+          <t>🟡 Опционально (1–2×)</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C58" s="8" t="n">
+        <v>294</v>
+      </c>
+      <c r="D58" s="8" t="n">
+        <v>287232</v>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>257066</v>
+      </c>
+      <c r="F58" s="8" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="18" t="inlineStr">
+        <is>
+          <t>🔴 НЕ трогать (затраты&gt;себест.)</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="n">
+        <v>47</v>
+      </c>
+      <c r="C59" s="11" t="n">
+        <v>5430</v>
+      </c>
+      <c r="D59" s="11" t="n">
+        <v>2058933</v>
+      </c>
+      <c r="E59" s="11" t="n">
+        <v>3591629</v>
+      </c>
+      <c r="F59" s="11" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="19" t="inlineStr">
+        <is>
+          <t>ВСЕГО</t>
+        </is>
+      </c>
+      <c r="B60" s="20" t="n">
+        <v>49</v>
+      </c>
+      <c r="C60" s="20" t="n">
+        <v>5724</v>
+      </c>
+      <c r="D60" s="20" t="n">
+        <v>2346164</v>
+      </c>
+      <c r="E60" s="20" t="n">
+        <v>3848695</v>
+      </c>
+      <c r="F60" s="20" t="n">
+        <v>0.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19383,46 +19908,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>Самовыкуп — итоги по фирмам (налог: Коротич 8%, КРОНА 6%)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
-        <is>
-          <t>Комиссия 41,5% · эквайринг 2,17% · логистика 90 ₽. @300 = цена выкупа 300 ₽ (СПП 4%); тек.цены = СПП по цене (≥2000:18%,1500-2000:12%,&lt;1500:4%).</t>
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>@300 = цена выкупа 300 ₽ (СПП 4%); тек.цены = СПП по цене. Комиссия 41,5% · эквайринг 2,17% · логистика 90 ₽.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>ВСЕ</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>Коротич</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t>КРОНА</t>
         </is>
@@ -19434,13 +19959,13 @@
           <t>SKU</t>
         </is>
       </c>
-      <c r="B5" s="18" t="n">
+      <c r="B5" s="24" t="n">
         <v>159</v>
       </c>
-      <c r="C5" s="18" t="n">
+      <c r="C5" s="24" t="n">
         <v>110</v>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="24" t="n">
         <v>49</v>
       </c>
     </row>
@@ -19450,13 +19975,13 @@
           <t>Остаток, шт</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="24" t="n">
         <v>13209</v>
       </c>
-      <c r="C6" s="18" t="n">
+      <c r="C6" s="24" t="n">
         <v>7485</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="24" t="n">
         <v>5724</v>
       </c>
     </row>
@@ -19466,17 +19991,17 @@
           <t>Себестоимость, ₽</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>5 908 446</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>3 562 281</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="24" t="inlineStr">
         <is>
           <t>2 346 164</t>
         </is>
@@ -19488,17 +20013,17 @@
           <t>Самовыкуп @300, ₽</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>3 032 178</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>1 736 894</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>1 295 284</t>
         </is>
@@ -19510,17 +20035,17 @@
           <t>Самовыкуп тек.цены, ₽</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>9 340 818</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t>5 492 124</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D9" s="24" t="inlineStr">
         <is>
           <t>3 848 695</t>
         </is>
@@ -19532,17 +20057,17 @@
           <t>Офиц. вывоз, ₽</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>3 366 933</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>1 941 512</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t>1 425 421</t>
         </is>
@@ -19551,36 +20076,36 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Парето@300 SKU</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="n">
+          <t>@300 🟢 SKU (≥2×)</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="n">
         <v>71</v>
       </c>
-      <c r="C11" s="18" t="n">
+      <c r="C11" s="24" t="n">
         <v>49</v>
       </c>
-      <c r="D11" s="18" t="n">
+      <c r="D11" s="24" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Парето@300: освобождаем ₽</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
+          <t>@300 🟢 освобождаем ₽</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>3 463 778</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>2 031 215</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D12" s="24" t="inlineStr">
         <is>
           <t>1 432 562</t>
         </is>
@@ -19589,20 +20114,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Парето@300: затраты ₽</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
+          <t>@300 🟢 затраты ₽</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>1 164 318</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>649 508</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="D13" s="24" t="inlineStr">
         <is>
           <t>514 810</t>
         </is>
@@ -19611,30 +20136,62 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Парето тек.цены SKU</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="18" t="n">
-        <v>0</v>
+          <t>@300 🟡 SKU (1–2×)</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="n">
+        <v>55</v>
+      </c>
+      <c r="C14" s="24" t="n">
+        <v>39</v>
+      </c>
+      <c r="D14" s="24" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>@300 🔴 SKU (&lt;1×)</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="n">
+        <v>33</v>
+      </c>
+      <c r="C15" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="D15" s="24" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>тек.цены 🔴 SKU (&lt;1×)</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="n">
+        <v>151</v>
+      </c>
+      <c r="C16" s="24" t="n">
+        <v>104</v>
+      </c>
+      <c r="D16" s="24" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t>Дешевле всего: самовыкуп@300 3 032 178 ₽ vs вывоз 3 366 933 ₽ (ниже на 334 755 ₽).</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="20" t="inlineStr">
-        <is>
-          <t>Самовыкуп по текущим ценам 9 340 818 ₽ — дороже вывоза в 2.8× (комиссия+налог на дорогих товарах). Не имеет смысла.</t>
+    <row r="19">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>Самовыкуп по текущим ценам 9 340 818 ₽ — дороже вывоза в 2.8×.</t>
         </is>
       </c>
     </row>
